--- a/outputs/detailed_multilingual.xlsx
+++ b/outputs/detailed_multilingual.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3374" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3359" uniqueCount="453">
   <si>
     <t>run_id</t>
   </si>
@@ -1363,7 +1363,7 @@
     <t>Sarvam</t>
   </si>
   <si>
-    <t>eleven_multilingual_v2</t>
+    <t>eleven_v3</t>
   </si>
   <si>
     <t>bulbul:v3</t>
@@ -1396,18 +1396,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7E4BC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -1439,8 +1433,8 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1738,9 +1732,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:O837"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="15" width="15.7109375" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
